--- a/Lab work/Lab4_Kuntal Das.xlsx
+++ b/Lab work/Lab4_Kuntal Das.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anudip Foundation\Lab work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C07993-18D2-456A-96FA-197C4A3066E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93863955-0AD9-460B-AF77-818DAD4C27DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,9 +81,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="[$-14009]yyyy/mm/dd;@"/>
+    <numFmt numFmtId="164" formatCode="[$-14009]yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -153,7 +153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -161,7 +161,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -212,238 +212,10 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{8347E748-A48F-4B95-8EFF-3F5E5BFCC0AA}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1649,27 +1421,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G16:J23">
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$G16="Product A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J40:J47">
-    <cfRule type="top10" dxfId="8" priority="4" rank="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J52:J59">
-    <cfRule type="expression" dxfId="7" priority="3">
-      <formula>AND($G52="Product B",$H52="North")</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I28:I35">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="between">
       <formula>45292</formula>
       <formula>45322</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J11">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThanOrEqual">
       <formula>150</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J40:J47">
+    <cfRule type="top10" dxfId="1" priority="4" rank="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J52:J59">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>AND($G52="Product B",$H52="North")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
